--- a/docs/downloads/04/tbl_raisons_non_scol_marovoay_madiromiongana.xlsx
+++ b/docs/downloads/04/tbl_raisons_non_scol_marovoay_madiromiongana.xlsx
@@ -387,12 +387,6 @@
           <t>Besoin revenu</t>
         </is>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>6.7</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -423,12 +417,6 @@
           <t>Paresse</t>
         </is>
       </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>10</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -459,12 +447,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>1.7</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -495,12 +477,6 @@
           <t>Besoin revenu</t>
         </is>
       </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>1.7</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -531,12 +507,6 @@
           <t>Handicap / maladie</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -549,12 +519,6 @@
           <t>Main-d'oeuvre exploitation</t>
         </is>
       </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11">
-        <v>3.3</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -602,12 +566,6 @@
         <is>
           <t>École trop éloignée</t>
         </is>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>0.8</v>
       </c>
     </row>
   </sheetData>
